--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OHIO_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/OHIO_2022.xlsx
@@ -3109,7 +3109,7 @@
         <v>34</v>
       </c>
       <c r="D153">
-        <v>0.009840810419681621</v>
+        <v>0.00984081041968162</v>
       </c>
     </row>
     <row r="154">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C175">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C181">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C452">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C475">
